--- a/cox/preogress.xlsx
+++ b/cox/preogress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lewis\OneDrive - The Ohio State University\Desktop\math\cox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307AEAA6-E2BB-4FD1-B1BB-8AEC9D605DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53593B3A-766B-450C-8815-068C53BD246A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75BD9C03-A5F2-4903-888C-3CBB1CF69E5A}"/>
   </bookViews>
@@ -345,11 +345,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -783,7 +783,7 @@
       <c r="A2" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="2" cm="1">
@@ -873,7 +873,7 @@
     </row>
     <row r="3" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="3" cm="1">
@@ -981,7 +981,7 @@
     </row>
     <row r="4" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="3" cm="1">
@@ -1093,7 +1093,7 @@
     </row>
     <row r="5" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="2" cm="1">
@@ -1209,7 +1209,7 @@
     </row>
     <row r="6" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" cm="1">
@@ -1320,10 +1320,10 @@
       <c r="BU6" s="2"/>
     </row>
     <row r="7" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" cm="1">
@@ -1410,8 +1410,8 @@
       <c r="BU7" s="2"/>
     </row>
     <row r="8" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="4" t="s">
+      <c r="A8" s="6"/>
+      <c r="B8" s="5" t="s">
         <v>60</v>
       </c>
       <c r="C8" s="3" cm="1">
@@ -1424,16 +1424,16 @@
       <c r="E8" s="2">
         <v>3</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="3">
         <v>4</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="3">
         <v>5</v>
       </c>
       <c r="H8" s="2">
         <v>6</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="3">
         <v>7</v>
       </c>
       <c r="J8" s="2">
@@ -1442,16 +1442,16 @@
       <c r="K8" s="2">
         <v>9</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="3">
         <v>10</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="3">
         <v>11</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="3">
         <v>12</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O8" s="3">
         <v>13</v>
       </c>
       <c r="P8" s="2"/>
@@ -1514,11 +1514,11 @@
       <c r="BU8" s="2"/>
     </row>
     <row r="9" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
+      <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="2" cm="1">
+      <c r="C9" s="3" cm="1">
         <f t="array" ref="C9:N9">_xlfn.SEQUENCE(1,12,1,1)</f>
         <v>1</v>
       </c>
@@ -1616,7 +1616,7 @@
       <c r="BU9" s="2"/>
     </row>
     <row r="10" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
+      <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
@@ -1716,7 +1716,7 @@
       <c r="BU10" s="2"/>
     </row>
     <row r="11" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
+      <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
         <v>9</v>
       </c>
@@ -1830,7 +1830,7 @@
       <c r="BU11" s="2"/>
     </row>
     <row r="12" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
+      <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
         <v>10</v>
       </c>
@@ -1934,7 +1934,7 @@
       <c r="BU12" s="2"/>
     </row>
     <row r="13" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
+      <c r="A13" s="6"/>
       <c r="B13" s="4" t="s">
         <v>11</v>
       </c>
@@ -2040,7 +2040,7 @@
       <c r="BU13" s="2"/>
     </row>
     <row r="14" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
+      <c r="A14" s="6"/>
       <c r="B14" s="4" t="s">
         <v>12</v>
       </c>
@@ -2142,7 +2142,7 @@
       <c r="BU14" s="2"/>
     </row>
     <row r="15" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
+      <c r="A15" s="6"/>
       <c r="B15" s="4" t="s">
         <v>13</v>
       </c>
@@ -2226,7 +2226,7 @@
       <c r="BU15" s="2"/>
     </row>
     <row r="16" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
+      <c r="A16" s="6"/>
       <c r="B16" s="4" t="s">
         <v>14</v>
       </c>
@@ -2330,7 +2330,7 @@
       <c r="BU16" s="2"/>
     </row>
     <row r="17" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>67</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -2428,7 +2428,7 @@
       <c r="BU17" s="2"/>
     </row>
     <row r="18" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
+      <c r="A18" s="6"/>
       <c r="B18" s="4" t="s">
         <v>16</v>
       </c>
@@ -2516,7 +2516,7 @@
       <c r="BU18" s="2"/>
     </row>
     <row r="19" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
+      <c r="A19" s="6"/>
       <c r="B19" s="4" t="s">
         <v>17</v>
       </c>
@@ -2624,7 +2624,7 @@
       <c r="BU19" s="2"/>
     </row>
     <row r="20" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
+      <c r="A20" s="6"/>
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -2742,7 +2742,7 @@
       <c r="BU20" s="2"/>
     </row>
     <row r="21" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
+      <c r="A21" s="6"/>
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -2834,7 +2834,7 @@
       <c r="BU21" s="2"/>
     </row>
     <row r="22" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
+      <c r="A22" s="6"/>
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -2956,7 +2956,7 @@
       <c r="BU22" s="2"/>
     </row>
     <row r="23" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="6" t="s">
         <v>68</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -3056,7 +3056,7 @@
       <c r="BU23" s="2"/>
     </row>
     <row r="24" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
+      <c r="A24" s="6"/>
       <c r="B24" s="4" t="s">
         <v>22</v>
       </c>
@@ -3168,7 +3168,7 @@
       <c r="BU24" s="2"/>
     </row>
     <row r="25" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
+      <c r="A25" s="6"/>
       <c r="B25" s="4" t="s">
         <v>62</v>
       </c>
@@ -3276,7 +3276,7 @@
       <c r="BU25" s="2"/>
     </row>
     <row r="26" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
+      <c r="A26" s="6"/>
       <c r="B26" s="4" t="s">
         <v>63</v>
       </c>
@@ -3402,7 +3402,7 @@
       <c r="BU26" s="2"/>
     </row>
     <row r="27" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
+      <c r="A27" s="6"/>
       <c r="B27" s="4" t="s">
         <v>23</v>
       </c>
@@ -3508,7 +3508,7 @@
       <c r="BU27" s="2"/>
     </row>
     <row r="28" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
+      <c r="A28" s="6"/>
       <c r="B28" s="4" t="s">
         <v>24</v>
       </c>
@@ -3606,7 +3606,7 @@
       <c r="BU28" s="2"/>
     </row>
     <row r="29" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
+      <c r="A29" s="6"/>
       <c r="B29" s="4" t="s">
         <v>25</v>
       </c>
@@ -3714,7 +3714,7 @@
       <c r="BU29" s="2"/>
     </row>
     <row r="30" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
+      <c r="A30" s="6"/>
       <c r="B30" s="4" t="s">
         <v>26</v>
       </c>
@@ -3820,7 +3820,7 @@
       <c r="BU30" s="2"/>
     </row>
     <row r="31" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
+      <c r="A31" s="6"/>
       <c r="B31" s="4" t="s">
         <v>27</v>
       </c>
@@ -3896,7 +3896,7 @@
       <c r="BU31" s="2"/>
     </row>
     <row r="32" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="6" t="s">
         <v>69</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -3996,7 +3996,7 @@
       <c r="BU32" s="2"/>
     </row>
     <row r="33" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
+      <c r="A33" s="6"/>
       <c r="B33" s="4" t="s">
         <v>29</v>
       </c>
@@ -4112,7 +4112,7 @@
       <c r="BU33" s="2"/>
     </row>
     <row r="34" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
+      <c r="A34" s="6"/>
       <c r="B34" s="4" t="s">
         <v>64</v>
       </c>
@@ -4218,7 +4218,7 @@
       <c r="BU34" s="2"/>
     </row>
     <row r="35" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
+      <c r="A35" s="6"/>
       <c r="B35" s="4" t="s">
         <v>30</v>
       </c>
@@ -4340,7 +4340,7 @@
       <c r="BU35" s="2"/>
     </row>
     <row r="36" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
+      <c r="A36" s="6"/>
       <c r="B36" s="4" t="s">
         <v>31</v>
       </c>
@@ -4446,7 +4446,7 @@
       <c r="BU36" s="2"/>
     </row>
     <row r="37" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A37" s="5"/>
+      <c r="A37" s="6"/>
       <c r="B37" s="4" t="s">
         <v>32</v>
       </c>
@@ -4560,7 +4560,7 @@
       <c r="BU37" s="2"/>
     </row>
     <row r="38" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>70</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -4652,7 +4652,7 @@
       <c r="BU38" s="2"/>
     </row>
     <row r="39" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
+      <c r="A39" s="6"/>
       <c r="B39" s="4" t="s">
         <v>34</v>
       </c>
@@ -4748,7 +4748,7 @@
       <c r="BU39" s="2"/>
     </row>
     <row r="40" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
+      <c r="A40" s="6"/>
       <c r="B40" s="4" t="s">
         <v>35</v>
       </c>
@@ -4868,7 +4868,7 @@
       <c r="BU40" s="2"/>
     </row>
     <row r="41" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
+      <c r="A41" s="6"/>
       <c r="B41" s="4" t="s">
         <v>36</v>
       </c>
@@ -4980,7 +4980,7 @@
       <c r="BU41" s="2"/>
     </row>
     <row r="42" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A42" s="5"/>
+      <c r="A42" s="6"/>
       <c r="B42" s="4" t="s">
         <v>37</v>
       </c>
@@ -5072,7 +5072,7 @@
       <c r="BU42" s="2"/>
     </row>
     <row r="43" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="6" t="s">
         <v>71</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -5192,7 +5192,7 @@
       <c r="BU43" s="2"/>
     </row>
     <row r="44" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A44" s="5"/>
+      <c r="A44" s="6"/>
       <c r="B44" s="4" t="s">
         <v>39</v>
       </c>
@@ -5302,7 +5302,7 @@
       <c r="BU44" s="2"/>
     </row>
     <row r="45" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A45" s="5"/>
+      <c r="A45" s="6"/>
       <c r="B45" s="4" t="s">
         <v>40</v>
       </c>
@@ -5404,7 +5404,7 @@
       <c r="BU45" s="2"/>
     </row>
     <row r="46" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A46" s="5"/>
+      <c r="A46" s="6"/>
       <c r="B46" s="4" t="s">
         <v>41</v>
       </c>
@@ -5514,7 +5514,7 @@
       <c r="BU46" s="2"/>
     </row>
     <row r="47" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="6" t="s">
         <v>72</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -5616,7 +5616,7 @@
       <c r="BU47" s="2"/>
     </row>
     <row r="48" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A48" s="5"/>
+      <c r="A48" s="6"/>
       <c r="B48" s="4" t="s">
         <v>43</v>
       </c>
@@ -5736,7 +5736,7 @@
       <c r="BU48" s="2"/>
     </row>
     <row r="49" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A49" s="5"/>
+      <c r="A49" s="6"/>
       <c r="B49" s="4" t="s">
         <v>44</v>
       </c>
@@ -5840,7 +5840,7 @@
       <c r="BU49" s="2"/>
     </row>
     <row r="50" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A50" s="5"/>
+      <c r="A50" s="6"/>
       <c r="B50" s="4" t="s">
         <v>45</v>
       </c>
@@ -5954,7 +5954,7 @@
       <c r="BU50" s="2"/>
     </row>
     <row r="51" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A51" s="5"/>
+      <c r="A51" s="6"/>
       <c r="B51" s="4" t="s">
         <v>46</v>
       </c>
@@ -6064,7 +6064,7 @@
       <c r="BU51" s="2"/>
     </row>
     <row r="52" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A52" s="5"/>
+      <c r="A52" s="6"/>
       <c r="B52" s="4" t="s">
         <v>47</v>
       </c>
@@ -6190,7 +6190,7 @@
       <c r="BU52" s="2"/>
     </row>
     <row r="53" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A53" s="5"/>
+      <c r="A53" s="6"/>
       <c r="B53" s="4" t="s">
         <v>48</v>
       </c>
@@ -6300,7 +6300,7 @@
       <c r="BU53" s="2"/>
     </row>
     <row r="54" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="6" t="s">
         <v>73</v>
       </c>
       <c r="B54" s="4" t="s">
@@ -6400,7 +6400,7 @@
       <c r="BU54" s="2"/>
     </row>
     <row r="55" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A55" s="5"/>
+      <c r="A55" s="6"/>
       <c r="B55" s="4" t="s">
         <v>50</v>
       </c>
@@ -6508,7 +6508,7 @@
       <c r="BU55" s="2"/>
     </row>
     <row r="56" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A56" s="5"/>
+      <c r="A56" s="6"/>
       <c r="B56" s="4" t="s">
         <v>51</v>
       </c>
@@ -6626,7 +6626,7 @@
       <c r="BU56" s="2"/>
     </row>
     <row r="57" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A57" s="5"/>
+      <c r="A57" s="6"/>
       <c r="B57" s="4" t="s">
         <v>52</v>
       </c>
@@ -6746,7 +6746,7 @@
       <c r="BU57" s="2"/>
     </row>
     <row r="58" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A58" s="5"/>
+      <c r="A58" s="6"/>
       <c r="B58" s="4" t="s">
         <v>53</v>
       </c>
@@ -6852,7 +6852,7 @@
       <c r="BU58" s="2"/>
     </row>
     <row r="59" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A59" s="5"/>
+      <c r="A59" s="6"/>
       <c r="B59" s="4" t="s">
         <v>54</v>
       </c>
@@ -6966,7 +6966,7 @@
       <c r="BU59" s="2"/>
     </row>
     <row r="60" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A60" s="5"/>
+      <c r="A60" s="6"/>
       <c r="B60" s="4" t="s">
         <v>55</v>
       </c>
@@ -7078,7 +7078,7 @@
       <c r="BU60" s="2"/>
     </row>
     <row r="61" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="6" t="s">
         <v>74</v>
       </c>
       <c r="B61" s="4" t="s">
@@ -7178,7 +7178,7 @@
       <c r="BU61" s="2"/>
     </row>
     <row r="62" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A62" s="5"/>
+      <c r="A62" s="6"/>
       <c r="B62" s="4" t="s">
         <v>57</v>
       </c>
@@ -7282,7 +7282,7 @@
       <c r="BU62" s="2"/>
     </row>
     <row r="63" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A63" s="5"/>
+      <c r="A63" s="6"/>
       <c r="B63" s="4" t="s">
         <v>58</v>
       </c>
@@ -7370,7 +7370,7 @@
       <c r="BU63" s="2"/>
     </row>
     <row r="64" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A64" s="5"/>
+      <c r="A64" s="6"/>
       <c r="B64" s="4" t="s">
         <v>59</v>
       </c>

--- a/cox/preogress.xlsx
+++ b/cox/preogress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lewis\OneDrive - The Ohio State University\Desktop\math\cox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53593B3A-766B-450C-8815-068C53BD246A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD90B4D-1AF4-4E2E-B7A6-1130190243F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75BD9C03-A5F2-4903-888C-3CBB1CF69E5A}"/>
   </bookViews>
@@ -1515,7 +1515,7 @@
     </row>
     <row r="9" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C9" s="3" cm="1">
@@ -1528,10 +1528,10 @@
       <c r="E9" s="2">
         <v>3</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>4</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="3">
         <v>5</v>
       </c>
       <c r="H9" s="2">
@@ -1540,19 +1540,19 @@
       <c r="I9" s="2">
         <v>7</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="3">
         <v>8</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="3">
         <v>9</v>
       </c>
       <c r="L9" s="2">
         <v>10</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="3">
         <v>11</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="3">
         <v>12</v>
       </c>
       <c r="O9" s="2"/>

--- a/cox/preogress.xlsx
+++ b/cox/preogress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lewis\OneDrive - The Ohio State University\Desktop\math\cox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD90B4D-1AF4-4E2E-B7A6-1130190243F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E2F145-93F3-467A-885C-17311F0B5819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75BD9C03-A5F2-4903-888C-3CBB1CF69E5A}"/>
   </bookViews>
@@ -1617,14 +1617,14 @@
     </row>
     <row r="10" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="2" cm="1">
+      <c r="C10" s="3" cm="1">
         <f t="array" ref="C10:M10">_xlfn.SEQUENCE(1,11,1,1)</f>
         <v>1</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
         <v>2</v>
       </c>
       <c r="E10" s="2">
@@ -1633,16 +1633,16 @@
       <c r="F10" s="2">
         <v>4</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="3">
         <v>5</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="3">
         <v>6</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="3">
         <v>7</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="3">
         <v>8</v>
       </c>
       <c r="K10" s="2">
@@ -1717,23 +1717,23 @@
     </row>
     <row r="11" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="2" cm="1">
+      <c r="C11" s="3" cm="1">
         <f t="array" ref="C11:T11">_xlfn.SEQUENCE(1,18,1,1)</f>
         <v>1</v>
       </c>
       <c r="D11" s="2">
         <v>2</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="3">
         <v>3</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
         <v>4</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="3">
         <v>5</v>
       </c>
       <c r="H11" s="2">
@@ -1748,31 +1748,31 @@
       <c r="K11" s="2">
         <v>9</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="3">
         <v>10</v>
       </c>
       <c r="M11" s="2">
         <v>11</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="3">
         <v>12</v>
       </c>
-      <c r="O11" s="2">
+      <c r="O11" s="3">
         <v>13</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="3">
         <v>14</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="3">
         <v>15</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R11" s="3">
         <v>16</v>
       </c>
       <c r="S11" s="2">
         <v>17</v>
       </c>
-      <c r="T11" s="2">
+      <c r="T11" s="3">
         <v>18</v>
       </c>
       <c r="U11" s="2"/>

--- a/cox/preogress.xlsx
+++ b/cox/preogress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lewis\OneDrive - The Ohio State University\Desktop\math\cox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E2F145-93F3-467A-885C-17311F0B5819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F2BA91-5322-4014-AE8F-A01C133EF620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75BD9C03-A5F2-4903-888C-3CBB1CF69E5A}"/>
+    <workbookView xWindow="3855" yWindow="1200" windowWidth="21600" windowHeight="11295" xr2:uid="{75BD9C03-A5F2-4903-888C-3CBB1CF69E5A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1831,20 +1831,20 @@
     </row>
     <row r="12" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="2" cm="1">
+      <c r="C12" s="3" cm="1">
         <f t="array" ref="C12:O12">_xlfn.SEQUENCE(1,13,1,1)</f>
         <v>1</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="3">
         <v>2</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="3">
         <v>3</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
         <v>4</v>
       </c>
       <c r="G12" s="2">
@@ -1853,25 +1853,25 @@
       <c r="H12" s="2">
         <v>6</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="3">
         <v>7</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="3">
         <v>8</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="3">
         <v>9</v>
       </c>
       <c r="L12" s="2">
         <v>10</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12" s="3">
         <v>11</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="3">
         <v>12</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="3">
         <v>13</v>
       </c>
       <c r="P12" s="2"/>
@@ -1948,7 +1948,7 @@
       <c r="E13" s="2">
         <v>3</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="3">
         <v>4</v>
       </c>
       <c r="G13" s="2">
